--- a/tasks/finalpool/canvas-assignment-deadline-gcal/groundtruth_workspace/Assignment_Tracker.xlsx
+++ b/tasks/finalpool/canvas-assignment-deadline-gcal/groundtruth_workspace/Assignment_Tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,11 +438,6 @@
           <t>Assignment_Group</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Submission_Count</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -463,9 +458,6 @@
           <t>Assignments (TMA)</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>930</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -486,9 +478,6 @@
           <t>Assignments (TMA)</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>782</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -509,9 +498,6 @@
           <t>Assignments (TMA)</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>713</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -532,9 +518,6 @@
           <t>Assignments (TMA)</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>617</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -555,9 +538,6 @@
           <t>Assignments (TMA)</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>526</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -578,9 +558,6 @@
           <t>Assignments (TMA)</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>450</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -600,9 +577,6 @@
         <is>
           <t>Final Exam</t>
         </is>
-      </c>
-      <c r="E8" t="n">
-        <v>524</v>
       </c>
     </row>
   </sheetData>
